--- a/nr-prepare-release/ig/StructureDefinition-AutorisationExercice.xlsx
+++ b/nr-prepare-release/ig/StructureDefinition-AutorisationExercice.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.1.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T07:37:42+00:00</t>
+    <t>2026-04-20T08:03:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-prepare-release/ig/StructureDefinition-AutorisationExercice.xlsx
+++ b/nr-prepare-release/ig/StructureDefinition-AutorisationExercice.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T08:03:20+00:00</t>
+    <t>2026-04-20T09:12:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
